--- a/Documentation/GanttChart.xlsx
+++ b/Documentation/GanttChart.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mamud\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mamud\Documents\GitHub\Mamud_Final_Year_Project\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC3E23B-4028-468C-98EE-B59DE1ADE213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAD10D97-180F-47E1-B831-18232C89FDDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3FE74159-537A-436B-86B1-03696786691A}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3FE74159-537A-436B-86B1-03696786691A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -221,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -237,7 +237,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -659,438 +658,437 @@
       <c r="U4" s="7"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
       <c r="K5" s="3">
         <v>45964</v>
       </c>
-      <c r="M5" s="14">
-        <v>2</v>
-      </c>
-      <c r="N5" s="14"/>
+      <c r="M5" s="13">
+        <v>2</v>
+      </c>
+      <c r="N5" s="13"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
+      <c r="H6" s="12"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
       <c r="K6" s="3">
         <v>45978</v>
       </c>
-      <c r="M6" s="14">
-        <v>2</v>
-      </c>
-      <c r="N6" s="14"/>
+      <c r="M6" s="13">
+        <v>2</v>
+      </c>
+      <c r="N6" s="13"/>
       <c r="O6" s="8"/>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
-      <c r="J7" s="13"/>
+      <c r="H7" s="12"/>
+      <c r="I7" s="12"/>
+      <c r="J7" s="12"/>
       <c r="K7" s="3">
         <v>45992</v>
       </c>
-      <c r="M7" s="14">
-        <v>2</v>
-      </c>
-      <c r="N7" s="14"/>
+      <c r="M7" s="13">
+        <v>2</v>
+      </c>
+      <c r="N7" s="13"/>
       <c r="P7" s="8"/>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="13"/>
-      <c r="C8" s="13"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
       <c r="D8" s="8"/>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
-      <c r="G8" s="13" t="s">
+      <c r="G8" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
-      <c r="J8" s="13"/>
+      <c r="H8" s="12"/>
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
       <c r="K8" s="3">
         <v>46006</v>
       </c>
-      <c r="M8" s="14">
-        <v>2</v>
-      </c>
-      <c r="N8" s="14"/>
+      <c r="M8" s="13">
+        <v>2</v>
+      </c>
+      <c r="N8" s="13"/>
       <c r="P8" s="8"/>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="14"/>
-      <c r="B9" s="14"/>
-      <c r="C9" s="14"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="Q9" s="11"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="M9" s="13"/>
+      <c r="N9" s="13"/>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="14"/>
       <c r="D10" s="9"/>
       <c r="E10" s="9"/>
       <c r="F10" s="9"/>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
       <c r="K10" s="3">
         <v>46020</v>
       </c>
-      <c r="M10" s="14">
-        <v>2</v>
-      </c>
-      <c r="N10" s="14"/>
+      <c r="M10" s="13">
+        <v>2</v>
+      </c>
+      <c r="N10" s="13"/>
       <c r="Q10" s="9"/>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
       <c r="D11" s="9"/>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
       <c r="K11" s="3">
         <v>46034</v>
       </c>
-      <c r="M11" s="14">
-        <v>2</v>
-      </c>
-      <c r="N11" s="14"/>
+      <c r="M11" s="13">
+        <v>2</v>
+      </c>
+      <c r="N11" s="13"/>
       <c r="Q11" s="9"/>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="14"/>
       <c r="D12" s="9"/>
       <c r="E12" s="9"/>
       <c r="F12" s="9"/>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H12" s="15"/>
-      <c r="I12" s="15"/>
-      <c r="J12" s="15"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
       <c r="K12" s="3">
         <v>46048</v>
       </c>
-      <c r="M12" s="14">
-        <v>2</v>
-      </c>
-      <c r="N12" s="14"/>
+      <c r="M12" s="13">
+        <v>2</v>
+      </c>
+      <c r="N12" s="13"/>
       <c r="R12" s="9"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
+      <c r="B13" s="14"/>
+      <c r="C13" s="14"/>
       <c r="D13" s="9"/>
       <c r="E13" s="9"/>
       <c r="F13" s="9"/>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="15"/>
-      <c r="I13" s="15"/>
-      <c r="J13" s="15"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="14"/>
       <c r="K13" s="3">
         <v>46062</v>
       </c>
-      <c r="M13" s="14">
-        <v>2</v>
-      </c>
-      <c r="N13" s="14"/>
+      <c r="M13" s="13">
+        <v>2</v>
+      </c>
+      <c r="N13" s="13"/>
       <c r="R13" s="9"/>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="13"/>
+      <c r="M14" s="13"/>
+      <c r="N14" s="13"/>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="16"/>
-      <c r="C15" s="16"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
       <c r="D15" s="10"/>
       <c r="E15" s="10"/>
       <c r="F15" s="10"/>
-      <c r="G15" s="16" t="s">
+      <c r="G15" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="16"/>
-      <c r="I15" s="16"/>
-      <c r="J15" s="16"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
       <c r="K15" s="3">
         <v>46076</v>
       </c>
-      <c r="M15" s="14">
-        <v>2</v>
-      </c>
-      <c r="N15" s="14"/>
+      <c r="M15" s="13">
+        <v>2</v>
+      </c>
+      <c r="N15" s="13"/>
       <c r="R15" s="10"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
       <c r="D16" s="10"/>
       <c r="E16" s="10"/>
       <c r="F16" s="10"/>
-      <c r="G16" s="16" t="s">
+      <c r="G16" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H16" s="16"/>
-      <c r="I16" s="16"/>
-      <c r="J16" s="16"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
       <c r="K16" s="3">
         <v>46090</v>
       </c>
-      <c r="M16" s="14">
-        <v>2</v>
-      </c>
-      <c r="N16" s="14"/>
+      <c r="M16" s="13">
+        <v>2</v>
+      </c>
+      <c r="N16" s="13"/>
       <c r="R16" s="10"/>
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
       <c r="D17" s="10"/>
       <c r="E17" s="10"/>
       <c r="F17" s="10"/>
-      <c r="G17" s="16" t="s">
+      <c r="G17" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
       <c r="K17" s="3">
         <v>46104</v>
       </c>
-      <c r="M17" s="14">
-        <v>2</v>
-      </c>
-      <c r="N17" s="14"/>
+      <c r="M17" s="13">
+        <v>2</v>
+      </c>
+      <c r="N17" s="13"/>
       <c r="S17" s="10"/>
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
       <c r="D18" s="10"/>
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
-      <c r="G18" s="16" t="s">
+      <c r="G18" s="15" t="s">
         <v>22</v>
       </c>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
       <c r="K18" s="3">
         <v>46118</v>
       </c>
-      <c r="M18" s="14">
-        <v>2</v>
-      </c>
-      <c r="N18" s="14"/>
+      <c r="M18" s="13">
+        <v>2</v>
+      </c>
+      <c r="N18" s="13"/>
       <c r="S18" s="10"/>
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
+      <c r="A19" s="13"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="13"/>
+      <c r="I19" s="13"/>
+      <c r="J19" s="13"/>
+      <c r="M19" s="13"/>
+      <c r="N19" s="13"/>
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="B20" s="17"/>
-      <c r="C20" s="17"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="17" t="s">
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H20" s="17"/>
-      <c r="I20" s="17"/>
-      <c r="J20" s="17"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
       <c r="K20" s="3">
         <v>46132</v>
       </c>
-      <c r="M20" s="14">
+      <c r="M20" s="13">
         <v>1</v>
       </c>
-      <c r="N20" s="14"/>
-      <c r="T20" s="12"/>
+      <c r="N20" s="13"/>
+      <c r="T20" s="11"/>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="16" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="17" t="s">
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H21" s="17"/>
-      <c r="I21" s="17"/>
-      <c r="J21" s="17"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
       <c r="K21" s="3">
         <v>46139</v>
       </c>
-      <c r="M21" s="14">
+      <c r="M21" s="13">
         <v>1</v>
       </c>
-      <c r="N21" s="14"/>
-      <c r="T21" s="12"/>
+      <c r="N21" s="13"/>
+      <c r="T21" s="11"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="17" t="s">
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H22" s="17"/>
-      <c r="I22" s="17"/>
-      <c r="J22" s="17"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
       <c r="K22" s="3">
         <v>46143</v>
       </c>
-      <c r="M22" s="14">
+      <c r="M22" s="13">
         <v>1</v>
       </c>
-      <c r="N22" s="14"/>
-      <c r="T22" s="12"/>
+      <c r="N22" s="13"/>
+      <c r="T22" s="11"/>
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="17" t="s">
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
-      <c r="J23" s="17"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
       <c r="K23" s="3">
         <v>46147</v>
       </c>
-      <c r="M23" s="14">
+      <c r="M23" s="13">
         <v>1</v>
       </c>
-      <c r="N23" s="14"/>
-      <c r="U23" s="12"/>
+      <c r="N23" s="13"/>
+      <c r="U23" s="11"/>
     </row>
     <row r="28" spans="1:21" ht="15.75" x14ac:dyDescent="0.25">
       <c r="D28" s="8"/>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="17" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="9"/>
-      <c r="I28" s="18" t="s">
+      <c r="I28" s="17" t="s">
         <v>21</v>
       </c>
       <c r="M28" s="10"/>
-      <c r="N28" s="18" t="s">
+      <c r="N28" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="Q28" s="12"/>
-      <c r="R28" s="18" t="s">
+      <c r="Q28" s="11"/>
+      <c r="R28" s="17" t="s">
         <v>23</v>
       </c>
     </row>
